--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,6 +917,809 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123198720</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90917</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>628374</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6895896</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123198460</v>
+      </c>
+      <c r="B5" t="n">
+        <v>88303</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>510</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cystostereum murrayi</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>628393</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6895973</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123198500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>628384</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6895982</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123211063</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hinrik-Hansbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>628408</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6895875</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123198564</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>628388</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6895967</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123198544</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>628383</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6895980</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123196227</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>628261</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6896031</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123198720</v>
+        <v>123198544</v>
       </c>
       <c r="B4" t="n">
-        <v>90917</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,38 +931,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628374</v>
+        <v>628383</v>
       </c>
       <c r="R4" t="n">
-        <v>6895896</v>
+        <v>6895980</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123198460</v>
+        <v>123198564</v>
       </c>
       <c r="B5" t="n">
-        <v>88303</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,34 +1057,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628393</v>
+        <v>628388</v>
       </c>
       <c r="R5" t="n">
-        <v>6895973</v>
+        <v>6895967</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1106,7 +1121,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1131,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1158,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123198500</v>
+        <v>123211063</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>57631</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,43 +1170,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628384</v>
+        <v>628408</v>
       </c>
       <c r="R6" t="n">
-        <v>6895982</v>
+        <v>6895875</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1221,19 +1235,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123211063</v>
+        <v>123198500</v>
       </c>
       <c r="B7" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1272,42 +1276,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628408</v>
+        <v>628384</v>
       </c>
       <c r="R7" t="n">
-        <v>6895875</v>
+        <v>6895982</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1337,9 +1342,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123198564</v>
+        <v>123196227</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,31 +1393,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628388</v>
+        <v>628261</v>
       </c>
       <c r="R8" t="n">
-        <v>6895967</v>
+        <v>6896031</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123198544</v>
+        <v>123198720</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>90917</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,43 +1510,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628383</v>
+        <v>628374</v>
       </c>
       <c r="R9" t="n">
-        <v>6895980</v>
+        <v>6895896</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,12 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123196227</v>
+        <v>123198460</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>88303</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,43 +1622,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628261</v>
+        <v>628393</v>
       </c>
       <c r="R10" t="n">
-        <v>6896031</v>
+        <v>6895973</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1381,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123196227</v>
+        <v>123198720</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>90917</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,43 +1393,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628261</v>
+        <v>628374</v>
       </c>
       <c r="R8" t="n">
-        <v>6896031</v>
+        <v>6895896</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1461,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123198720</v>
+        <v>123196227</v>
       </c>
       <c r="B9" t="n">
-        <v>90917</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,38 +1505,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628374</v>
+        <v>628261</v>
       </c>
       <c r="R9" t="n">
-        <v>6895896</v>
+        <v>6896031</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123198544</v>
+        <v>123211063</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,39 +935,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628383</v>
+        <v>628408</v>
       </c>
       <c r="R4" t="n">
-        <v>6895980</v>
+        <v>6895875</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,24 +996,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123198564</v>
+        <v>123198460</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>88303</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,39 +1041,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628388</v>
+        <v>628393</v>
       </c>
       <c r="R5" t="n">
-        <v>6895967</v>
+        <v>6895973</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1121,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123211063</v>
+        <v>123196227</v>
       </c>
       <c r="B6" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,42 +1149,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628408</v>
+        <v>628261</v>
       </c>
       <c r="R6" t="n">
-        <v>6895875</v>
+        <v>6896031</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1235,9 +1215,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123198500</v>
+        <v>123198544</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,31 +1266,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1309,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628384</v>
+        <v>628383</v>
       </c>
       <c r="R7" t="n">
-        <v>6895982</v>
+        <v>6895980</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1344,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1344,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1493,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123196227</v>
+        <v>123198564</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,31 +1500,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1538,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628261</v>
+        <v>628388</v>
       </c>
       <c r="R9" t="n">
-        <v>6896031</v>
+        <v>6895967</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1573,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123198460</v>
+        <v>123198500</v>
       </c>
       <c r="B10" t="n">
-        <v>88303</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,38 +1617,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628393</v>
+        <v>628384</v>
       </c>
       <c r="R10" t="n">
-        <v>6895973</v>
+        <v>6895982</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123211063</v>
+        <v>123196227</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,42 +931,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628408</v>
+        <v>628261</v>
       </c>
       <c r="R4" t="n">
-        <v>6895875</v>
+        <v>6896031</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,9 +997,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123198460</v>
+        <v>123198720</v>
       </c>
       <c r="B5" t="n">
-        <v>88303</v>
+        <v>90917</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,25 +1048,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628393</v>
+        <v>628374</v>
       </c>
       <c r="R5" t="n">
-        <v>6895973</v>
+        <v>6895896</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1100,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123196227</v>
+        <v>123198564</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,31 +1160,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1182,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628261</v>
+        <v>628388</v>
       </c>
       <c r="R6" t="n">
-        <v>6896031</v>
+        <v>6895967</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1217,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123198544</v>
+        <v>123198500</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>98365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,31 +1277,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628383</v>
+        <v>628384</v>
       </c>
       <c r="R7" t="n">
-        <v>6895980</v>
+        <v>6895982</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,12 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123198720</v>
+        <v>123211063</v>
       </c>
       <c r="B8" t="n">
-        <v>90917</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,38 +1394,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628374</v>
+        <v>628408</v>
       </c>
       <c r="R8" t="n">
-        <v>6895896</v>
+        <v>6895875</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1449,19 +1459,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:44</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,7 +1488,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123198564</v>
+        <v>123198544</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628388</v>
+        <v>628383</v>
       </c>
       <c r="R9" t="n">
-        <v>6895967</v>
+        <v>6895980</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1578,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123198500</v>
+        <v>123198460</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>88303</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,43 +1622,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628384</v>
+        <v>628393</v>
       </c>
       <c r="R10" t="n">
-        <v>6895982</v>
+        <v>6895973</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123196227</v>
+        <v>123211063</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,43 +931,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628261</v>
+        <v>628408</v>
       </c>
       <c r="R4" t="n">
-        <v>6896031</v>
+        <v>6895875</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,19 +996,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123198720</v>
+        <v>123196227</v>
       </c>
       <c r="B5" t="n">
-        <v>90917</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,38 +1037,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628374</v>
+        <v>628261</v>
       </c>
       <c r="R5" t="n">
-        <v>6895896</v>
+        <v>6896031</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123198564</v>
+        <v>123198460</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>88306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,39 +1158,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628388</v>
+        <v>628393</v>
       </c>
       <c r="R6" t="n">
-        <v>6895967</v>
+        <v>6895973</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1228,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123198500</v>
+        <v>123198564</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,31 +1266,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1310,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628384</v>
+        <v>628388</v>
       </c>
       <c r="R7" t="n">
-        <v>6895982</v>
+        <v>6895967</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1345,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123211063</v>
+        <v>123198720</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>90920</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,42 +1383,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628408</v>
+        <v>628374</v>
       </c>
       <c r="R8" t="n">
-        <v>6895875</v>
+        <v>6895896</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1459,9 +1444,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,7 +1486,7 @@
         <v>123198544</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1610,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123198460</v>
+        <v>123198500</v>
       </c>
       <c r="B10" t="n">
-        <v>88303</v>
+        <v>98368</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,38 +1617,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628393</v>
+        <v>628384</v>
       </c>
       <c r="R10" t="n">
-        <v>6895973</v>
+        <v>6895982</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123211063</v>
+        <v>123198500</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,42 +931,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628408</v>
+        <v>628384</v>
       </c>
       <c r="R4" t="n">
-        <v>6895875</v>
+        <v>6895982</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,9 +997,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123196227</v>
+        <v>123198544</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,31 +1048,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628261</v>
+        <v>628383</v>
       </c>
       <c r="R5" t="n">
-        <v>6896031</v>
+        <v>6895980</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1126,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1161,7 @@
         <v>123198460</v>
       </c>
       <c r="B6" t="n">
-        <v>88306</v>
+        <v>88308</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1254,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123198564</v>
+        <v>123196227</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,31 +1282,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628388</v>
+        <v>628261</v>
       </c>
       <c r="R7" t="n">
-        <v>6895967</v>
+        <v>6896031</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123198720</v>
+        <v>123211063</v>
       </c>
       <c r="B8" t="n">
-        <v>90920</v>
+        <v>57634</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,38 +1399,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628374</v>
+        <v>628408</v>
       </c>
       <c r="R8" t="n">
-        <v>6895896</v>
+        <v>6895875</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1444,19 +1464,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:44</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,7 +1493,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123198544</v>
+        <v>123198564</v>
       </c>
       <c r="B9" t="n">
         <v>57481</v>
@@ -1528,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628383</v>
+        <v>628388</v>
       </c>
       <c r="R9" t="n">
-        <v>6895980</v>
+        <v>6895967</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,12 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123198500</v>
+        <v>123198720</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>90922</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,43 +1622,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628384</v>
+        <v>628374</v>
       </c>
       <c r="R10" t="n">
-        <v>6895982</v>
+        <v>6895896</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123198500</v>
+        <v>123198544</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,31 +931,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628384</v>
+        <v>628383</v>
       </c>
       <c r="R4" t="n">
-        <v>6895982</v>
+        <v>6895980</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123198544</v>
+        <v>123211063</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,39 +1057,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628383</v>
+        <v>628408</v>
       </c>
       <c r="R5" t="n">
-        <v>6895980</v>
+        <v>6895875</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1114,24 +1118,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123198460</v>
+        <v>123198564</v>
       </c>
       <c r="B6" t="n">
-        <v>88308</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,34 +1163,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628393</v>
+        <v>628388</v>
       </c>
       <c r="R6" t="n">
-        <v>6895973</v>
+        <v>6895967</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1233,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1237,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1270,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123196227</v>
+        <v>123198460</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>88310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,43 +1276,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628261</v>
+        <v>628393</v>
       </c>
       <c r="R7" t="n">
-        <v>6896031</v>
+        <v>6895973</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1387,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123211063</v>
+        <v>123198720</v>
       </c>
       <c r="B8" t="n">
-        <v>57634</v>
+        <v>90928</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,42 +1388,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628408</v>
+        <v>628374</v>
       </c>
       <c r="R8" t="n">
-        <v>6895875</v>
+        <v>6895896</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1464,9 +1449,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123198564</v>
+        <v>123196227</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>98376</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,31 +1500,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1538,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628388</v>
+        <v>628261</v>
       </c>
       <c r="R9" t="n">
-        <v>6895967</v>
+        <v>6896031</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1573,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123198720</v>
+        <v>123198500</v>
       </c>
       <c r="B10" t="n">
-        <v>90922</v>
+        <v>98376</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,38 +1617,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628374</v>
+        <v>628384</v>
       </c>
       <c r="R10" t="n">
-        <v>6895896</v>
+        <v>6895982</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123198544</v>
+        <v>123198720</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>90931</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,43 +931,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628383</v>
+        <v>628374</v>
       </c>
       <c r="R4" t="n">
-        <v>6895980</v>
+        <v>6895896</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -999,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123211063</v>
+        <v>123198500</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
+        <v>98379</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,42 +1043,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628408</v>
+        <v>628384</v>
       </c>
       <c r="R5" t="n">
-        <v>6895875</v>
+        <v>6895982</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1118,9 +1109,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123198564</v>
+        <v>123198460</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>88313</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,39 +1164,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628388</v>
+        <v>628393</v>
       </c>
       <c r="R6" t="n">
-        <v>6895967</v>
+        <v>6895973</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123198460</v>
+        <v>123196227</v>
       </c>
       <c r="B7" t="n">
-        <v>88310</v>
+        <v>98379</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,38 +1272,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628393</v>
+        <v>628261</v>
       </c>
       <c r="R7" t="n">
-        <v>6895973</v>
+        <v>6896031</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1376,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123198720</v>
+        <v>123198544</v>
       </c>
       <c r="B8" t="n">
-        <v>90928</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,38 +1389,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628374</v>
+        <v>628383</v>
       </c>
       <c r="R8" t="n">
-        <v>6895896</v>
+        <v>6895980</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1451,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1467,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123196227</v>
+        <v>123211063</v>
       </c>
       <c r="B9" t="n">
-        <v>98376</v>
+        <v>57634</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,43 +1511,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628261</v>
+        <v>628408</v>
       </c>
       <c r="R9" t="n">
-        <v>6896031</v>
+        <v>6895875</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1566,19 +1576,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123198500</v>
+        <v>123198564</v>
       </c>
       <c r="B10" t="n">
-        <v>98376</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,31 +1617,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628384</v>
+        <v>628388</v>
       </c>
       <c r="R10" t="n">
-        <v>6895982</v>
+        <v>6895967</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123198720</v>
+        <v>123198564</v>
       </c>
       <c r="B4" t="n">
-        <v>90931</v>
+        <v>57487</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,38 +931,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628374</v>
+        <v>628388</v>
       </c>
       <c r="R4" t="n">
-        <v>6895896</v>
+        <v>6895967</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -994,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,7 +1039,7 @@
         <v>123198500</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1148,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123198460</v>
+        <v>123198720</v>
       </c>
       <c r="B6" t="n">
-        <v>88313</v>
+        <v>90948</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,25 +1165,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628393</v>
+        <v>628374</v>
       </c>
       <c r="R6" t="n">
-        <v>6895973</v>
+        <v>6895896</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1223,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,7 +1268,7 @@
         <v>123196227</v>
       </c>
       <c r="B7" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1377,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123198544</v>
+        <v>123211063</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>57640</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,39 +1398,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628383</v>
+        <v>628408</v>
       </c>
       <c r="R8" t="n">
-        <v>6895980</v>
+        <v>6895875</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1455,24 +1459,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123211063</v>
+        <v>123198544</v>
       </c>
       <c r="B9" t="n">
-        <v>57634</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,38 +1504,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628408</v>
+        <v>628383</v>
       </c>
       <c r="R9" t="n">
-        <v>6895875</v>
+        <v>6895980</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1576,9 +1566,24 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123198564</v>
+        <v>123198460</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
+        <v>88330</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,39 +1626,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628388</v>
+        <v>628393</v>
       </c>
       <c r="R10" t="n">
-        <v>6895967</v>
+        <v>6895973</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123198544</v>
+        <v>123198460</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>88330</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,39 +1504,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628383</v>
+        <v>628393</v>
       </c>
       <c r="R9" t="n">
-        <v>6895980</v>
+        <v>6895973</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1568,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,12 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123198460</v>
+        <v>123198544</v>
       </c>
       <c r="B10" t="n">
-        <v>88330</v>
+        <v>57487</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,34 +1616,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628393</v>
+        <v>628383</v>
       </c>
       <c r="R10" t="n">
-        <v>6895973</v>
+        <v>6895980</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1685,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1690,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1488,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123198460</v>
+        <v>123198544</v>
       </c>
       <c r="B9" t="n">
-        <v>88330</v>
+        <v>57487</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,34 +1504,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628393</v>
+        <v>628383</v>
       </c>
       <c r="R9" t="n">
-        <v>6895973</v>
+        <v>6895980</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1578,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123198544</v>
+        <v>123198460</v>
       </c>
       <c r="B10" t="n">
-        <v>57487</v>
+        <v>88330</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,39 +1626,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628383</v>
+        <v>628393</v>
       </c>
       <c r="R10" t="n">
-        <v>6895980</v>
+        <v>6895973</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1680,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,12 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123198564</v>
+        <v>123198500</v>
       </c>
       <c r="B4" t="n">
-        <v>57487</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,31 +931,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628388</v>
+        <v>628384</v>
       </c>
       <c r="R4" t="n">
-        <v>6895967</v>
+        <v>6895982</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123198500</v>
+        <v>123198564</v>
       </c>
       <c r="B5" t="n">
-        <v>98396</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,31 +1048,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628384</v>
+        <v>628388</v>
       </c>
       <c r="R5" t="n">
-        <v>6895982</v>
+        <v>6895967</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123198720</v>
+        <v>123196227</v>
       </c>
       <c r="B6" t="n">
-        <v>90948</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,38 +1165,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628374</v>
+        <v>628261</v>
       </c>
       <c r="R6" t="n">
-        <v>6895896</v>
+        <v>6896031</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1228,7 +1233,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1243,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123196227</v>
+        <v>123198720</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>90953</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,43 +1282,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628261</v>
+        <v>628374</v>
       </c>
       <c r="R7" t="n">
-        <v>6896031</v>
+        <v>6895896</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123211063</v>
+        <v>123198544</v>
       </c>
       <c r="B8" t="n">
-        <v>57640</v>
+        <v>57490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,38 +1398,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628408</v>
+        <v>628383</v>
       </c>
       <c r="R8" t="n">
-        <v>6895875</v>
+        <v>6895980</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1459,9 +1460,24 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1504,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123198544</v>
+        <v>123198460</v>
       </c>
       <c r="B9" t="n">
-        <v>57487</v>
+        <v>88335</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,39 +1520,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628383</v>
+        <v>628393</v>
       </c>
       <c r="R9" t="n">
-        <v>6895980</v>
+        <v>6895973</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1568,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,12 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123198460</v>
+        <v>123211063</v>
       </c>
       <c r="B10" t="n">
-        <v>88330</v>
+        <v>57643</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,34 +1632,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628393</v>
+        <v>628408</v>
       </c>
       <c r="R10" t="n">
-        <v>6895973</v>
+        <v>6895875</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1683,19 +1693,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123198500</v>
+        <v>123211063</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,43 +931,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628384</v>
+        <v>628408</v>
       </c>
       <c r="R4" t="n">
-        <v>6895982</v>
+        <v>6895875</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -997,19 +996,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123198564</v>
+        <v>123196227</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
+        <v>98504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,31 +1037,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1081,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628388</v>
+        <v>628261</v>
       </c>
       <c r="R5" t="n">
-        <v>6895967</v>
+        <v>6896031</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1126,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123196227</v>
+        <v>123198500</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628261</v>
+        <v>628384</v>
       </c>
       <c r="R6" t="n">
-        <v>6896031</v>
+        <v>6895982</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1233,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1243,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,7 +1262,7 @@
         <v>123198720</v>
       </c>
       <c r="B7" t="n">
-        <v>90953</v>
+        <v>90955</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1382,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123198544</v>
+        <v>123198460</v>
       </c>
       <c r="B8" t="n">
-        <v>57490</v>
+        <v>88337</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,39 +1387,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628383</v>
+        <v>628393</v>
       </c>
       <c r="R8" t="n">
-        <v>6895980</v>
+        <v>6895973</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1462,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1472,12 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123198460</v>
+        <v>123198564</v>
       </c>
       <c r="B9" t="n">
-        <v>88335</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,34 +1499,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628393</v>
+        <v>628388</v>
       </c>
       <c r="R9" t="n">
-        <v>6895973</v>
+        <v>6895967</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1579,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123211063</v>
+        <v>123198544</v>
       </c>
       <c r="B10" t="n">
-        <v>57643</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,38 +1616,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628408</v>
+        <v>628383</v>
       </c>
       <c r="R10" t="n">
-        <v>6895875</v>
+        <v>6895980</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1693,9 +1678,24 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1371,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123198460</v>
+        <v>123198564</v>
       </c>
       <c r="B8" t="n">
-        <v>88337</v>
+        <v>57491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,34 +1387,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628393</v>
+        <v>628388</v>
       </c>
       <c r="R8" t="n">
-        <v>6895973</v>
+        <v>6895967</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123198564</v>
+        <v>123198460</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
+        <v>88337</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,39 +1504,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628388</v>
+        <v>628393</v>
       </c>
       <c r="R9" t="n">
-        <v>6895967</v>
+        <v>6895973</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123211063</v>
+        <v>123198460</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
+        <v>88337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,38 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628408</v>
+        <v>628393</v>
       </c>
       <c r="R4" t="n">
-        <v>6895875</v>
+        <v>6895973</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,9 +992,19 @@
           <t>2025-03-14</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123196227</v>
+        <v>123198544</v>
       </c>
       <c r="B5" t="n">
-        <v>98504</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,31 +1043,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628261</v>
+        <v>628383</v>
       </c>
       <c r="R5" t="n">
-        <v>6896031</v>
+        <v>6895980</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1105,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1156,7 @@
         <v>123198500</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1259,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123198720</v>
+        <v>123196227</v>
       </c>
       <c r="B7" t="n">
-        <v>90955</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,38 +1282,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628374</v>
+        <v>628261</v>
       </c>
       <c r="R7" t="n">
-        <v>6895896</v>
+        <v>6896031</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1334,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1387,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123198564</v>
+        <v>123198720</v>
       </c>
       <c r="B8" t="n">
-        <v>57491</v>
+        <v>90955</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,43 +1399,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628388</v>
+        <v>628374</v>
       </c>
       <c r="R8" t="n">
-        <v>6895967</v>
+        <v>6895896</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1451,7 +1462,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1472,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1499,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123198460</v>
+        <v>123198564</v>
       </c>
       <c r="B9" t="n">
-        <v>88337</v>
+        <v>57491</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,34 +1515,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628393</v>
+        <v>628388</v>
       </c>
       <c r="R9" t="n">
-        <v>6895973</v>
+        <v>6895967</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1589,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123198544</v>
+        <v>123211063</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>57644</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,39 +1632,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628383</v>
+        <v>628408</v>
       </c>
       <c r="R10" t="n">
-        <v>6895980</v>
+        <v>6895875</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1678,24 +1693,9 @@
           <t>2025-03-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1034,12 +1034,7 @@
         <v>123198544</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1502,12 +1497,7 @@
         <v>123198564</v>
       </c>
       <c r="B9" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>123198544</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>123198564</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,6 +1710,598 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133653186</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gruvdammen, Gruvdammen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>628332</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6895939</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133652789</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gruvdammen, Gruvdammen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>628246</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6896017</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133652773</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gruvdammen, Gruvdammen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>628252</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6896012</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133654388</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gruvdammen, Gruvdammen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>628332</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6895974</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133653645</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gruvdammen, Gruvdammen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>628367</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6895924</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Alldeles färska ringhack i basen på en gran</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133653338</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gruvdammen, Gruvdammen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>628318</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6895913</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1906,32 +1906,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133652773</v>
+        <v>133654388</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>96348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628252</v>
+        <v>628332</v>
       </c>
       <c r="R13" t="n">
-        <v>6896012</v>
+        <v>6895974</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133654388</v>
+        <v>133652773</v>
       </c>
       <c r="B14" t="n">
-        <v>96348</v>
+        <v>91918</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628332</v>
+        <v>628252</v>
       </c>
       <c r="R14" t="n">
-        <v>6895974</v>
+        <v>6896012</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1906,32 +1906,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133654388</v>
+        <v>133652773</v>
       </c>
       <c r="B13" t="n">
-        <v>96348</v>
+        <v>91918</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628332</v>
+        <v>628252</v>
       </c>
       <c r="R13" t="n">
-        <v>6895974</v>
+        <v>6896012</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133652773</v>
+        <v>133654388</v>
       </c>
       <c r="B14" t="n">
-        <v>91918</v>
+        <v>96348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628252</v>
+        <v>628332</v>
       </c>
       <c r="R14" t="n">
-        <v>6896012</v>
+        <v>6895974</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1906,32 +1906,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133654388</v>
+        <v>133652773</v>
       </c>
       <c r="B13" t="n">
-        <v>96348</v>
+        <v>91918</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628332</v>
+        <v>628252</v>
       </c>
       <c r="R13" t="n">
-        <v>6895974</v>
+        <v>6896012</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133652773</v>
+        <v>133654388</v>
       </c>
       <c r="B14" t="n">
-        <v>91918</v>
+        <v>96348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628252</v>
+        <v>628332</v>
       </c>
       <c r="R14" t="n">
-        <v>6896012</v>
+        <v>6895974</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2302,6 +2302,200 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133815640</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91881</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kulåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>628250</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6896008</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133815641</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91918</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kulåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>628255</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6896019</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1715,7 +1715,7 @@
         <v>133653186</v>
       </c>
       <c r="B11" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>133652789</v>
       </c>
       <c r="B12" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>133652773</v>
       </c>
       <c r="B13" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>133654388</v>
       </c>
       <c r="B14" t="n">
-        <v>96348</v>
+        <v>96350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>133653338</v>
       </c>
       <c r="B16" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>133815640</v>
       </c>
       <c r="B17" t="n">
-        <v>91881</v>
+        <v>91883</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>133815641</v>
       </c>
       <c r="B18" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -2307,7 +2307,7 @@
         <v>133815640</v>
       </c>
       <c r="B17" t="n">
-        <v>91883</v>
+        <v>91889</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>133815641</v>
       </c>
       <c r="B18" t="n">
-        <v>91920</v>
+        <v>91926</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1715,7 +1715,7 @@
         <v>133653186</v>
       </c>
       <c r="B11" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>133652789</v>
       </c>
       <c r="B12" t="n">
-        <v>91883</v>
+        <v>91891</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>133652773</v>
       </c>
       <c r="B13" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>133654388</v>
       </c>
       <c r="B14" t="n">
-        <v>96350</v>
+        <v>96358</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>133653338</v>
       </c>
       <c r="B16" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>133815640</v>
       </c>
       <c r="B17" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>133815641</v>
       </c>
       <c r="B18" t="n">
-        <v>91926</v>
+        <v>91928</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1715,7 +1715,7 @@
         <v>133653186</v>
       </c>
       <c r="B11" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>133652789</v>
       </c>
       <c r="B12" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>133652773</v>
       </c>
       <c r="B13" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>133654388</v>
       </c>
       <c r="B14" t="n">
-        <v>96358</v>
+        <v>96386</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>133653645</v>
       </c>
       <c r="B15" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>133653338</v>
       </c>
       <c r="B16" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>133815640</v>
       </c>
       <c r="B17" t="n">
-        <v>91891</v>
+        <v>91910</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>133815641</v>
       </c>
       <c r="B18" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1906,32 +1906,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133652773</v>
+        <v>133654388</v>
       </c>
       <c r="B13" t="n">
-        <v>91947</v>
+        <v>96386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628252</v>
+        <v>628332</v>
       </c>
       <c r="R13" t="n">
-        <v>6896012</v>
+        <v>6895974</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133654388</v>
+        <v>133652773</v>
       </c>
       <c r="B14" t="n">
-        <v>96386</v>
+        <v>91947</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628332</v>
+        <v>628252</v>
       </c>
       <c r="R14" t="n">
-        <v>6895974</v>
+        <v>6896012</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1715,7 +1715,7 @@
         <v>133653186</v>
       </c>
       <c r="B11" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>133652789</v>
       </c>
       <c r="B12" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>133654388</v>
       </c>
       <c r="B13" t="n">
-        <v>96386</v>
+        <v>96396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>133652773</v>
       </c>
       <c r="B14" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>133653645</v>
       </c>
       <c r="B15" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>133653338</v>
       </c>
       <c r="B16" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>133815640</v>
       </c>
       <c r="B17" t="n">
-        <v>91910</v>
+        <v>91920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>133815641</v>
       </c>
       <c r="B18" t="n">
-        <v>91947</v>
+        <v>91957</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1906,32 +1906,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133654388</v>
+        <v>133652773</v>
       </c>
       <c r="B13" t="n">
-        <v>96396</v>
+        <v>91957</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628332</v>
+        <v>628252</v>
       </c>
       <c r="R13" t="n">
-        <v>6895974</v>
+        <v>6896012</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133652773</v>
+        <v>133654388</v>
       </c>
       <c r="B14" t="n">
-        <v>91957</v>
+        <v>96396</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628252</v>
+        <v>628332</v>
       </c>
       <c r="R14" t="n">
-        <v>6896012</v>
+        <v>6895974</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1906,32 +1906,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133652773</v>
+        <v>133654388</v>
       </c>
       <c r="B13" t="n">
-        <v>91957</v>
+        <v>96396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628252</v>
+        <v>628332</v>
       </c>
       <c r="R13" t="n">
-        <v>6896012</v>
+        <v>6895974</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133654388</v>
+        <v>133652773</v>
       </c>
       <c r="B14" t="n">
-        <v>96396</v>
+        <v>91957</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628332</v>
+        <v>628252</v>
       </c>
       <c r="R14" t="n">
-        <v>6895974</v>
+        <v>6896012</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1715,7 +1715,7 @@
         <v>133653186</v>
       </c>
       <c r="B11" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>133652789</v>
       </c>
       <c r="B12" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>133654388</v>
       </c>
       <c r="B13" t="n">
-        <v>96396</v>
+        <v>96398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>133652773</v>
       </c>
       <c r="B14" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2210,7 +2210,7 @@
         <v>133653338</v>
       </c>
       <c r="B16" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>133815640</v>
       </c>
       <c r="B17" t="n">
-        <v>91920</v>
+        <v>91922</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>133815641</v>
       </c>
       <c r="B18" t="n">
-        <v>91957</v>
+        <v>91959</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1906,32 +1906,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133654388</v>
+        <v>133652773</v>
       </c>
       <c r="B13" t="n">
-        <v>96399</v>
+        <v>91960</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628332</v>
+        <v>628252</v>
       </c>
       <c r="R13" t="n">
-        <v>6895974</v>
+        <v>6896012</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133652773</v>
+        <v>133654388</v>
       </c>
       <c r="B14" t="n">
-        <v>91960</v>
+        <v>96399</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628252</v>
+        <v>628332</v>
       </c>
       <c r="R14" t="n">
-        <v>6896012</v>
+        <v>6895974</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -1715,7 +1715,7 @@
         <v>133653186</v>
       </c>
       <c r="B11" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
         <v>133652789</v>
       </c>
       <c r="B12" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1906,32 +1906,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133652773</v>
+        <v>133654388</v>
       </c>
       <c r="B13" t="n">
-        <v>91960</v>
+        <v>96406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1941,10 +1941,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628252</v>
+        <v>628332</v>
       </c>
       <c r="R13" t="n">
-        <v>6896012</v>
+        <v>6895974</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133654388</v>
+        <v>133652773</v>
       </c>
       <c r="B14" t="n">
-        <v>96399</v>
+        <v>91967</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628332</v>
+        <v>628252</v>
       </c>
       <c r="R14" t="n">
-        <v>6895974</v>
+        <v>6896012</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2210,7 +2210,7 @@
         <v>133653338</v>
       </c>
       <c r="B16" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>133815640</v>
       </c>
       <c r="B17" t="n">
-        <v>91923</v>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2404,7 +2404,7 @@
         <v>133815641</v>
       </c>
       <c r="B18" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,63 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108926170</v>
+        <v>123198460</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gruvdammen, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>628257.7709504579</v>
+        <v>628393</v>
       </c>
       <c r="R2" t="n">
-        <v>6896051.324841533</v>
+        <v>6895973</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,75 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108923592</v>
+        <v>133652773</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gruvdammen, Mpd</t>
+          <t>Gruvdammen, Gruvdammen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>628362.9907459437</v>
+        <v>628252</v>
       </c>
       <c r="R3" t="n">
-        <v>6895845.852644746</v>
+        <v>6896012</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:40</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:40</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,27 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123198460</v>
+        <v>133653186</v>
       </c>
       <c r="B4" t="n">
-        <v>88337</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,34 +890,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Gruvdammen, Gruvdammen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>628393</v>
+        <v>628332</v>
       </c>
       <c r="R4" t="n">
-        <v>6895973</v>
+        <v>6895939</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,22 +944,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,22 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123198544</v>
+        <v>133815641</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,39 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Kulåsen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>628383</v>
+        <v>628255</v>
       </c>
       <c r="R5" t="n">
-        <v>6895980</v>
+        <v>6896019</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,27 +1041,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:39</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:39</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,67 +1061,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123198500</v>
+        <v>133654388</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Gruvdammen, Gruvdammen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>628384</v>
+        <v>628332</v>
       </c>
       <c r="R6" t="n">
-        <v>6895982</v>
+        <v>6895974</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1223,22 +1138,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,67 +1158,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123196227</v>
+        <v>123198720</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>628261</v>
+        <v>628374</v>
       </c>
       <c r="R7" t="n">
-        <v>6896031</v>
+        <v>6895896</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1345,7 +1240,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1250,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,15 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123198720</v>
+        <v>133652789</v>
       </c>
       <c r="B8" t="n">
-        <v>90955</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91937</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,17 +1308,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Gruvdammen, Gruvdammen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>628374</v>
+        <v>628246</v>
       </c>
       <c r="R8" t="n">
-        <v>6895896</v>
+        <v>6896017</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1452,22 +1342,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:44</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:44</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,62 +1362,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123198564</v>
+        <v>133815640</v>
       </c>
       <c r="B9" t="n">
-        <v>57741</v>
+        <v>91937</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Galtström, Galtström, Mpd</t>
+          <t>Kulåsen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>628388</v>
+        <v>628250</v>
       </c>
       <c r="R9" t="n">
-        <v>6895967</v>
+        <v>6896008</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1564,22 +1439,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,66 +1459,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123211063</v>
+        <v>133654315</v>
       </c>
       <c r="B10" t="n">
-        <v>57644</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hinrik-Hansbäcken, Mpd</t>
+          <t>Gruvdammen, Gruvdammen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>628408</v>
+        <v>628391</v>
       </c>
       <c r="R10" t="n">
-        <v>6895875</v>
+        <v>6895994</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1680,12 +1536,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,22 +1556,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olle Finnström</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133653186</v>
+        <v>123198544</v>
       </c>
       <c r="B11" t="n">
-        <v>91967</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,34 +1579,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gruvdammen, Gruvdammen, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>628332</v>
+        <v>628383</v>
       </c>
       <c r="R11" t="n">
-        <v>6895939</v>
+        <v>6895980</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1777,12 +1638,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på död gran, därför svårt att avgöra ålder</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,60 +1673,65 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133652789</v>
+        <v>123198564</v>
       </c>
       <c r="B12" t="n">
-        <v>91930</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gruvdammen, Gruvdammen, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>628246</v>
+        <v>628388</v>
       </c>
       <c r="R12" t="n">
-        <v>6896017</v>
+        <v>6895967</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1874,12 +1755,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,57 +1785,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133654388</v>
+        <v>133653645</v>
       </c>
       <c r="B13" t="n">
-        <v>96406</v>
+        <v>57975</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gruvdammen, Gruvdammen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>628332</v>
+        <v>628367</v>
       </c>
       <c r="R13" t="n">
-        <v>6895974</v>
+        <v>6895924</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1977,6 +1873,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Alldeles färska ringhack i basen på en gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,48 +1904,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133652773</v>
+        <v>108926489</v>
       </c>
       <c r="B14" t="n">
-        <v>91967</v>
+        <v>58327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gruvdammen, Gruvdammen, Mpd</t>
+          <t>Gruvdammen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>628252</v>
+        <v>628275</v>
       </c>
       <c r="R14" t="n">
-        <v>6896012</v>
+        <v>6896043</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2068,12 +1975,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,22 +2005,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133653645</v>
+        <v>123211063</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,39 +2028,38 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gruvdammen, Gruvdammen, Mpd</t>
+          <t>Hinrik-Hansbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>628367</v>
+        <v>628408</v>
       </c>
       <c r="R15" t="n">
-        <v>6895924</v>
+        <v>6895875</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2170,17 +2086,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Alldeles färska ringhack i basen på en gran</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,22 +2106,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Olle Finnström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133653338</v>
+        <v>108923592</v>
       </c>
       <c r="B16" t="n">
-        <v>99188</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2235,20 +2146,30 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gruvdammen, Gruvdammen, Mpd</t>
+          <t>Gruvdammen, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>628318</v>
+        <v>628363</v>
       </c>
       <c r="R16" t="n">
-        <v>6895913</v>
+        <v>6895846</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2272,12 +2193,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2292,60 +2223,70 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133815640</v>
+        <v>108926170</v>
       </c>
       <c r="B17" t="n">
-        <v>91930</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kulåsen, Mpd</t>
+          <t>Gruvdammen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>628250</v>
+        <v>628257</v>
       </c>
       <c r="R17" t="n">
-        <v>6896008</v>
+        <v>6896051</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2369,12 +2310,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,60 +2340,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133815641</v>
+        <v>123196121</v>
       </c>
       <c r="B18" t="n">
-        <v>91967</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kulåsen, Mpd</t>
+          <t>Galtström, Galtström, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>628255</v>
+        <v>628307</v>
       </c>
       <c r="R18" t="n">
-        <v>6896019</v>
+        <v>6896031</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2466,12 +2422,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2486,15 +2452,446 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123196227</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>628261</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6896031</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123198500</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Galtström, Galtström, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>628384</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6895982</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133653338</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gruvdammen, Gruvdammen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>628318</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6895913</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Viktor Persson</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Viktor Persson</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123211071</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hinrik-Hansbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>628380</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6896001</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Njurunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4878-2025 artfynd.xlsx
+++ b/artfynd/A 4878-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123198460</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133652773</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133653186</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133815641</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133654388</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123198720</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133652789</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133815640</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133654315</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123198544</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1794,6 +1849,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123198564</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1901,6 +1961,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133653645</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2014,6 +2079,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108926489</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2115,6 +2185,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123211063</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2232,6 +2307,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108923592</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2349,6 +2429,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108926170</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2461,6 +2546,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123196121</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2573,6 +2663,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123196227</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2685,6 +2780,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123198500</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2782,6 +2882,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133653338</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2892,8 +2997,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123211071</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>